--- a/Business Case Data My Analysis.xlsx
+++ b/Business Case Data My Analysis.xlsx
@@ -1598,57 +1598,60 @@
     <xf numFmtId="10" fontId="18" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1723,9 +1726,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1734,108 +1734,6 @@
     <cellStyle name="Note" xfId="2" builtinId="10"/>
   </cellStyles>
   <dxfs count="46">
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2042,6 +1940,108 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
       <border diagonalUp="1">
@@ -2419,7 +2419,7 @@
     <dataField name="Average of CSAT" fld="7" subtotal="average" baseField="9" baseItem="0" numFmtId="2"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="13">
+    <format dxfId="44">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="9" count="1">
@@ -2428,10 +2428,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="43">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="42">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="9" count="1">
@@ -2440,7 +2440,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="10">
+    <format dxfId="41">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -2457,47 +2457,47 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{98EE68BE-7E15-4398-85BE-A165118A4EBF}" name="Table3" displayName="Table3" ref="B13:O26" totalsRowCount="1" headerRowDxfId="44" headerRowBorderDxfId="43" tableBorderDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{98EE68BE-7E15-4398-85BE-A165118A4EBF}" name="Table3" displayName="Table3" ref="B13:O26" totalsRowCount="1" headerRowDxfId="30" headerRowBorderDxfId="29" tableBorderDxfId="28">
   <autoFilter ref="B13:O25" xr:uid="{98EE68BE-7E15-4398-85BE-A165118A4EBF}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B14:O25">
     <sortCondition ref="B13:B25"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{13369F0F-3AB1-4E19-AEA4-74AB8FA4AC07}" name="Month" totalsRowLabel="SUM" dataDxfId="41" totalsRowDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{91C05C52-F979-405E-83F8-F4F4FB8334A7}" name="Monthly Ticket Profit" totalsRowFunction="sum" dataDxfId="39" totalsRowDxfId="38">
+    <tableColumn id="1" xr3:uid="{13369F0F-3AB1-4E19-AEA4-74AB8FA4AC07}" name="Month" totalsRowLabel="SUM" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{91C05C52-F979-405E-83F8-F4F4FB8334A7}" name="Monthly Ticket Profit" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="24">
       <calculatedColumnFormula>$J$8*$C$8*'Original Data'!B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{05F66680-ABCF-4596-8230-023C8649C9B7}" name="Monthly Popcorn Profit" totalsRowFunction="sum" dataDxfId="37" totalsRowDxfId="36">
+    <tableColumn id="3" xr3:uid="{05F66680-ABCF-4596-8230-023C8649C9B7}" name="Monthly Popcorn Profit" totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="22">
       <calculatedColumnFormula>$J$8*$D$8*'Original Data'!C2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6297BAA9-424E-4D87-AC2F-4849FC81D718}" name="Monthly Soda Profit" totalsRowFunction="sum" dataDxfId="35" totalsRowDxfId="34">
+    <tableColumn id="4" xr3:uid="{6297BAA9-424E-4D87-AC2F-4849FC81D718}" name="Monthly Soda Profit" totalsRowFunction="sum" dataDxfId="21" totalsRowDxfId="20">
       <calculatedColumnFormula>$J$8*$E$8*'Original Data'!D2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{E82A0C0E-5460-4577-999A-BE35AE65B55E}" name="Monthly Food Profit" totalsRowFunction="custom" dataDxfId="33" totalsRowDxfId="32">
+    <tableColumn id="5" xr3:uid="{E82A0C0E-5460-4577-999A-BE35AE65B55E}" name="Monthly Food Profit" totalsRowFunction="custom" dataDxfId="19" totalsRowDxfId="18">
       <calculatedColumnFormula>$J$8*$F$8*'Original Data'!E2</calculatedColumnFormula>
       <totalsRowFormula>SUM(Table3[Monthly Food Profit])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{68C8FE79-3376-4D6A-B586-4E64258C3F48}" name="Total Month Profit" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="30">
+    <tableColumn id="6" xr3:uid="{68C8FE79-3376-4D6A-B586-4E64258C3F48}" name="Total Month Profit" totalsRowFunction="custom" dataDxfId="17" totalsRowDxfId="16">
       <calculatedColumnFormula>SUM(C14:F14)</calculatedColumnFormula>
       <totalsRowFormula>SUM(Table3[Total Month Profit])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{0D0C992D-E3FB-4279-8159-B38D227BC07E}" name="Waiting Time" dataDxfId="29" totalsRowDxfId="28"/>
-    <tableColumn id="12" xr3:uid="{CCFC953D-DEC7-45DD-8448-2016D119E477}" name="CSAT" dataDxfId="27" totalsRowDxfId="26"/>
-    <tableColumn id="13" xr3:uid="{FD5BCCE2-C2F1-4E05-91AD-79E2113FD122}" name="Main Detractors (Original)" dataDxfId="25" totalsRowDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{F572158B-F5CA-447F-AAC5-11DB2B9C27F3}" name="Main Detractors (Derived)" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{31BB3ADD-02EA-44ED-87EE-8A8908420295}" name="Monthly Customers" totalsRowFunction="custom" dataDxfId="21" totalsRowDxfId="20">
+    <tableColumn id="11" xr3:uid="{0D0C992D-E3FB-4279-8159-B38D227BC07E}" name="Waiting Time" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{CCFC953D-DEC7-45DD-8448-2016D119E477}" name="CSAT" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="13" xr3:uid="{FD5BCCE2-C2F1-4E05-91AD-79E2113FD122}" name="Main Detractors (Original)" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{F572158B-F5CA-447F-AAC5-11DB2B9C27F3}" name="Main Detractors (Derived)" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{31BB3ADD-02EA-44ED-87EE-8A8908420295}" name="Monthly Customers" totalsRowFunction="custom" dataDxfId="7" totalsRowDxfId="6">
       <calculatedColumnFormula>'Original Data'!B2*$J$8</calculatedColumnFormula>
       <totalsRowFormula>SUM(Table3[Monthly Customers])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00FD6420-2D19-46EC-AC28-02A996E479ED}" name="Monthly Popcorn Sales" totalsRowFunction="custom" dataDxfId="19" totalsRowDxfId="18">
+    <tableColumn id="10" xr3:uid="{00FD6420-2D19-46EC-AC28-02A996E479ED}" name="Monthly Popcorn Sales" totalsRowFunction="custom" dataDxfId="5" totalsRowDxfId="4">
       <calculatedColumnFormula>'Original Data'!C2*$J$8</calculatedColumnFormula>
       <totalsRowFormula>SUM(Table3[Monthly Popcorn Sales])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{95BBC102-F817-4660-85A8-658300664494}" name="Monthly Soda Sales" totalsRowFunction="custom" dataDxfId="17" totalsRowDxfId="16">
+    <tableColumn id="14" xr3:uid="{95BBC102-F817-4660-85A8-658300664494}" name="Monthly Soda Sales" totalsRowFunction="custom" dataDxfId="3" totalsRowDxfId="2">
       <calculatedColumnFormula>'Original Data'!D2*$J$8</calculatedColumnFormula>
       <totalsRowFormula>SUM(Table3[Monthly Soda Sales])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{C2D64A4B-4C7D-4EF8-BDF8-0739120165FA}" name="Monthly Food Sales" totalsRowFunction="custom" dataDxfId="15" totalsRowDxfId="14">
+    <tableColumn id="15" xr3:uid="{C2D64A4B-4C7D-4EF8-BDF8-0739120165FA}" name="Monthly Food Sales" totalsRowFunction="custom" dataDxfId="1" totalsRowDxfId="0">
       <calculatedColumnFormula>'Original Data'!E2*$J$8</calculatedColumnFormula>
       <totalsRowFormula>SUM(Table3[Monthly Food Sales])</totalsRowFormula>
     </tableColumn>
@@ -2510,8 +2510,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F60740D7-29AD-4637-B62D-F9179738F5B7}" name="Table1" displayName="Table1" ref="B11:C15" totalsRowShown="0">
   <autoFilter ref="B11:C15" xr:uid="{F60740D7-29AD-4637-B62D-F9179738F5B7}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{26905DF3-F256-4440-8A7B-0031322D227F}" name="Item" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{CBB190AA-C096-4F28-B909-6EDE53B89FD9}" name="Precentage" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{26905DF3-F256-4440-8A7B-0031322D227F}" name="Item" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{CBB190AA-C096-4F28-B909-6EDE53B89FD9}" name="Precentage" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2521,8 +2521,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{643B47FE-4CDD-4A56-8FDF-2DB5B920508F}" name="Table2" displayName="Table2" ref="B6:C8" totalsRowShown="0">
   <autoFilter ref="B6:C8" xr:uid="{643B47FE-4CDD-4A56-8FDF-2DB5B920508F}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{668963EA-2F77-4C89-B864-BC7EABD4C495}" name="Division" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{56F5A29F-2C60-44B1-B952-B67616A3BE18}" name="Precentage" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{668963EA-2F77-4C89-B864-BC7EABD4C495}" name="Division" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{56F5A29F-2C60-44B1-B952-B67616A3BE18}" name="Precentage" dataDxfId="37">
       <calculatedColumnFormula>SUM(Table3[[#Totals],[Monthly Popcorn Profit]:[Monthly Food Profit]])/Table3[[#Totals],[Total Month Profit]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2531,17 +2531,17 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{9E9D13BE-EE33-4006-9AAD-ED72E0393CF5}" name="Table6" displayName="Table6" ref="B33:E46" totalsRowShown="0" headerRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{9E9D13BE-EE33-4006-9AAD-ED72E0393CF5}" name="Table6" displayName="Table6" ref="B33:E46" totalsRowShown="0" headerRowDxfId="36">
   <autoFilter ref="B33:E46" xr:uid="{9E9D13BE-EE33-4006-9AAD-ED72E0393CF5}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{E5465A40-2F55-4000-B9D7-F62866409E8C}" name="Months" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{AD653C3E-1E96-4651-A710-CC0B82BD0BE2}" name="Customers/Employee Ratio" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{E5465A40-2F55-4000-B9D7-F62866409E8C}" name="Months" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{AD653C3E-1E96-4651-A710-CC0B82BD0BE2}" name="Customers/Employee Ratio" dataDxfId="34">
       <calculatedColumnFormula>('Monthly Profit &amp; Refined Data'!L14/'Monthly Profit &amp; Refined Data'!$G$8)/30</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{33CEF8CF-DC1E-41E8-AB58-1DB87F34FA72}" name="Daily Cust." dataDxfId="0">
+    <tableColumn id="3" xr3:uid="{33CEF8CF-DC1E-41E8-AB58-1DB87F34FA72}" name="Daily Cust." dataDxfId="33">
       <calculatedColumnFormula>'Monthly Profit &amp; Refined Data'!L14/30</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F8EB7C1E-9F37-4719-8CCB-1C9BD6E943A2}" name="Wait Time" dataDxfId="2">
+    <tableColumn id="4" xr3:uid="{F8EB7C1E-9F37-4719-8CCB-1C9BD6E943A2}" name="Wait Time" dataDxfId="32">
       <calculatedColumnFormula>'Monthly Profit &amp; Refined Data'!H14</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2550,7 +2550,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{615E2AAB-3BB9-42DA-8DAA-BE8EEE60E497}" name="Table7" displayName="Table7" ref="B19:C22" totalsRowShown="0" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{615E2AAB-3BB9-42DA-8DAA-BE8EEE60E497}" name="Table7" displayName="Table7" ref="B19:C22" totalsRowShown="0" tableBorderDxfId="31">
   <autoFilter ref="B19:C22" xr:uid="{615E2AAB-3BB9-42DA-8DAA-BE8EEE60E497}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{BE6F9202-9809-4243-9B84-6E29FA9FCCCA}" name="Item"/>
@@ -3583,33 +3583,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="93" t="s">
+      <c r="C2" s="109" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="I2" s="93" t="s">
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+      <c r="I2" s="109" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="93"/>
+      <c r="J2" s="109"/>
     </row>
     <row r="3" spans="2:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="109"/>
     </row>
     <row r="4" spans="2:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
     </row>
     <row r="5" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="15"/>
@@ -3709,12 +3709,12 @@
       <c r="D11" s="14"/>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
-      <c r="L11" s="94" t="s">
+      <c r="L11" s="110" t="s">
         <v>69</v>
       </c>
-      <c r="M11" s="94"/>
-      <c r="N11" s="94"/>
-      <c r="O11" s="94"/>
+      <c r="M11" s="110"/>
+      <c r="N11" s="110"/>
+      <c r="O11" s="110"/>
       <c r="P11" s="50"/>
     </row>
     <row r="12" spans="2:16" ht="14.4" x14ac:dyDescent="0.25">
@@ -4545,20 +4545,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="108" t="s">
+      <c r="B2" s="94" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="108"/>
+      <c r="C2" s="94"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="108"/>
-      <c r="C3" s="108"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
     </row>
     <row r="5" spans="2:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="96" t="s">
+      <c r="B5" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="96"/>
+      <c r="C5" s="104"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
@@ -4587,10 +4587,10 @@
       </c>
     </row>
     <row r="10" spans="2:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="96" t="s">
+      <c r="B10" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="96"/>
+      <c r="C10" s="104"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
@@ -4626,11 +4626,11 @@
         <f>Table3[[#Totals],[Monthly Soda Profit]]/Table3[[#Totals],[Total Month Profit]]</f>
         <v>0.15131674354073824</v>
       </c>
-      <c r="E14" s="97" t="s">
+      <c r="E14" s="95" t="s">
         <v>85</v>
       </c>
-      <c r="F14" s="98"/>
-      <c r="G14" s="99"/>
+      <c r="F14" s="96"/>
+      <c r="G14" s="97"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="11" t="s">
@@ -4640,32 +4640,32 @@
         <f>Table3[[#Totals],[Monthly Food Profit]]/Table3[[#Totals],[Total Month Profit]]</f>
         <v>9.5270458928467097E-2</v>
       </c>
-      <c r="E15" s="100"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="102"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="100"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E16" s="100"/>
-      <c r="F16" s="101"/>
-      <c r="G16" s="102"/>
+      <c r="E16" s="98"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="100"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="96" t="s">
+      <c r="B17" s="104" t="s">
         <v>81</v>
       </c>
-      <c r="C17" s="96"/>
-      <c r="E17" s="100"/>
-      <c r="F17" s="101"/>
-      <c r="G17" s="102"/>
+      <c r="C17" s="104"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="100"/>
     </row>
     <row r="18" spans="2:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="109" t="s">
+      <c r="B18" s="105" t="s">
         <v>107</v>
       </c>
-      <c r="C18" s="109"/>
-      <c r="E18" s="100"/>
-      <c r="F18" s="101"/>
-      <c r="G18" s="102"/>
+      <c r="C18" s="105"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="100"/>
     </row>
     <row r="19" spans="2:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="59" t="s">
@@ -4674,9 +4674,9 @@
       <c r="C19" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="103"/>
-      <c r="F19" s="104"/>
-      <c r="G19" s="105"/>
+      <c r="E19" s="101"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="103"/>
     </row>
     <row r="20" spans="2:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="55" t="s">
@@ -4707,10 +4707,10 @@
     </row>
     <row r="23" spans="2:7" ht="23.4" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="96" t="s">
+      <c r="B24" s="104" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="96"/>
+      <c r="C24" s="104"/>
     </row>
     <row r="25" spans="2:7" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="11" t="s">
@@ -4727,11 +4727,11 @@
       <c r="C26" s="48">
         <v>4.2</v>
       </c>
-      <c r="E26" s="97" t="s">
+      <c r="E26" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="F26" s="98"/>
-      <c r="G26" s="99"/>
+      <c r="F26" s="96"/>
+      <c r="G26" s="97"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="11" t="s">
@@ -4740,9 +4740,9 @@
       <c r="C27" s="48">
         <v>2.25</v>
       </c>
-      <c r="E27" s="100"/>
-      <c r="F27" s="101"/>
-      <c r="G27" s="102"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="99"/>
+      <c r="G27" s="100"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="11" t="s">
@@ -4751,9 +4751,9 @@
       <c r="C28" s="48">
         <v>7.333333333333333</v>
       </c>
-      <c r="E28" s="100"/>
-      <c r="F28" s="101"/>
-      <c r="G28" s="102"/>
+      <c r="E28" s="98"/>
+      <c r="F28" s="99"/>
+      <c r="G28" s="100"/>
     </row>
     <row r="29" spans="2:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="11" t="s">
@@ -4762,25 +4762,25 @@
       <c r="C29" s="48">
         <v>4.333333333333333</v>
       </c>
-      <c r="E29" s="103"/>
-      <c r="F29" s="104"/>
-      <c r="G29" s="105"/>
+      <c r="E29" s="101"/>
+      <c r="F29" s="102"/>
+      <c r="G29" s="103"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="96" t="s">
+      <c r="B31" s="104" t="s">
         <v>113</v>
       </c>
-      <c r="C31" s="96"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="96"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="104"/>
+      <c r="E31" s="104"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="95" t="s">
+      <c r="B32" s="106" t="s">
         <v>88</v>
       </c>
-      <c r="C32" s="95"/>
-      <c r="D32" s="95"/>
-      <c r="E32" s="95"/>
+      <c r="C32" s="106"/>
+      <c r="D32" s="106"/>
+      <c r="E32" s="106"/>
     </row>
     <row r="33" spans="2:11" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="11" t="s">
@@ -4846,13 +4846,13 @@
         <f>'Monthly Profit &amp; Refined Data'!H16</f>
         <v>8</v>
       </c>
-      <c r="G36" s="97" t="s">
+      <c r="G36" s="95" t="s">
         <v>90</v>
       </c>
-      <c r="H36" s="98"/>
-      <c r="I36" s="98"/>
-      <c r="J36" s="98"/>
-      <c r="K36" s="99"/>
+      <c r="H36" s="96"/>
+      <c r="I36" s="96"/>
+      <c r="J36" s="96"/>
+      <c r="K36" s="97"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="52">
@@ -4870,11 +4870,11 @@
         <f>'Monthly Profit &amp; Refined Data'!H17</f>
         <v>21</v>
       </c>
-      <c r="G37" s="100"/>
-      <c r="H37" s="101"/>
-      <c r="I37" s="101"/>
-      <c r="J37" s="101"/>
-      <c r="K37" s="102"/>
+      <c r="G37" s="98"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="99"/>
+      <c r="J37" s="99"/>
+      <c r="K37" s="100"/>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="52">
@@ -4892,11 +4892,11 @@
         <f>'Monthly Profit &amp; Refined Data'!H18</f>
         <v>25</v>
       </c>
-      <c r="G38" s="100"/>
-      <c r="H38" s="101"/>
-      <c r="I38" s="101"/>
-      <c r="J38" s="101"/>
-      <c r="K38" s="102"/>
+      <c r="G38" s="98"/>
+      <c r="H38" s="99"/>
+      <c r="I38" s="99"/>
+      <c r="J38" s="99"/>
+      <c r="K38" s="100"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="52">
@@ -4914,11 +4914,11 @@
         <f>'Monthly Profit &amp; Refined Data'!H19</f>
         <v>10</v>
       </c>
-      <c r="G39" s="100"/>
-      <c r="H39" s="101"/>
-      <c r="I39" s="101"/>
-      <c r="J39" s="101"/>
-      <c r="K39" s="102"/>
+      <c r="G39" s="98"/>
+      <c r="H39" s="99"/>
+      <c r="I39" s="99"/>
+      <c r="J39" s="99"/>
+      <c r="K39" s="100"/>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" s="52">
@@ -4936,11 +4936,11 @@
         <f>'Monthly Profit &amp; Refined Data'!H20</f>
         <v>15</v>
       </c>
-      <c r="G40" s="100"/>
-      <c r="H40" s="101"/>
-      <c r="I40" s="101"/>
-      <c r="J40" s="101"/>
-      <c r="K40" s="102"/>
+      <c r="G40" s="98"/>
+      <c r="H40" s="99"/>
+      <c r="I40" s="99"/>
+      <c r="J40" s="99"/>
+      <c r="K40" s="100"/>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="52">
@@ -4958,11 +4958,11 @@
         <f>'Monthly Profit &amp; Refined Data'!H21</f>
         <v>8</v>
       </c>
-      <c r="G41" s="100"/>
-      <c r="H41" s="101"/>
-      <c r="I41" s="101"/>
-      <c r="J41" s="101"/>
-      <c r="K41" s="102"/>
+      <c r="G41" s="98"/>
+      <c r="H41" s="99"/>
+      <c r="I41" s="99"/>
+      <c r="J41" s="99"/>
+      <c r="K41" s="100"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="52">
@@ -4980,11 +4980,11 @@
         <f>'Monthly Profit &amp; Refined Data'!H22</f>
         <v>6</v>
       </c>
-      <c r="G42" s="100"/>
-      <c r="H42" s="101"/>
-      <c r="I42" s="101"/>
-      <c r="J42" s="101"/>
-      <c r="K42" s="102"/>
+      <c r="G42" s="98"/>
+      <c r="H42" s="99"/>
+      <c r="I42" s="99"/>
+      <c r="J42" s="99"/>
+      <c r="K42" s="100"/>
     </row>
     <row r="43" spans="2:11" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="52">
@@ -5002,11 +5002,11 @@
         <f>'Monthly Profit &amp; Refined Data'!H23</f>
         <v>18</v>
       </c>
-      <c r="G43" s="103"/>
-      <c r="H43" s="104"/>
-      <c r="I43" s="104"/>
-      <c r="J43" s="104"/>
-      <c r="K43" s="105"/>
+      <c r="G43" s="101"/>
+      <c r="H43" s="102"/>
+      <c r="I43" s="102"/>
+      <c r="J43" s="102"/>
+      <c r="K43" s="103"/>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="52">
@@ -5043,7 +5043,7 @@
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B46" s="135" t="s">
+      <c r="B46" s="93" t="s">
         <v>89</v>
       </c>
       <c r="C46" s="46">
@@ -5055,17 +5055,17 @@
         <v>142.71693121693124</v>
       </c>
       <c r="E46" s="46">
-        <f t="shared" ref="D46:E46" si="0">AVERAGE(E34:E45)</f>
+        <f t="shared" ref="E46" si="0">AVERAGE(E34:E45)</f>
         <v>13</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="107"/>
-      <c r="C48" s="107"/>
+      <c r="B48" s="108"/>
+      <c r="C48" s="108"/>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="106"/>
-      <c r="C49" s="106"/>
+      <c r="B49" s="107"/>
+      <c r="C49" s="107"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="11"/>
@@ -5125,6 +5125,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="G36:K43"/>
+    <mergeCell ref="E14:G19"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B48:C48"/>
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="E26:G29"/>
     <mergeCell ref="B17:C17"/>
@@ -5132,12 +5138,6 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="G36:K43"/>
-    <mergeCell ref="E14:G19"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B48:C48"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5190,12 +5190,12 @@
       <c r="C3" s="87">
         <v>0.2</v>
       </c>
-      <c r="E3" s="110" t="s">
+      <c r="E3" s="111" t="s">
         <v>101</v>
       </c>
-      <c r="F3" s="111"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="111"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="112"/>
       <c r="I3" s="66">
         <f>'Monthly Profit &amp; Refined Data'!$L$26</f>
         <v>51378.095238095244</v>
@@ -5221,34 +5221,34 @@
     </row>
     <row r="7" spans="1:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:15" ht="49.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="125" t="s">
+      <c r="B8" s="126" t="s">
         <v>111</v>
       </c>
-      <c r="C8" s="126"/>
-      <c r="D8" s="126"/>
-      <c r="E8" s="126"/>
-      <c r="F8" s="126"/>
-      <c r="G8" s="127"/>
-      <c r="I8" s="125" t="s">
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="127"/>
+      <c r="G8" s="128"/>
+      <c r="I8" s="126" t="s">
         <v>108</v>
       </c>
-      <c r="J8" s="126"/>
-      <c r="K8" s="126"/>
-      <c r="L8" s="126"/>
-      <c r="M8" s="126"/>
-      <c r="N8" s="126"/>
-      <c r="O8" s="127"/>
+      <c r="J8" s="127"/>
+      <c r="K8" s="127"/>
+      <c r="L8" s="127"/>
+      <c r="M8" s="127"/>
+      <c r="N8" s="127"/>
+      <c r="O8" s="128"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
-      <c r="C10" s="123" t="s">
+      <c r="C10" s="124" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="124"/>
-      <c r="E10" s="124"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
       <c r="F10" s="82">
         <f>SUM('Monthly Profit &amp; Refined Data'!$C$8:$E$8)</f>
         <v>11.75</v>
@@ -5278,11 +5278,11 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C12" s="123" t="s">
+      <c r="C12" s="124" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="124"/>
-      <c r="E12" s="124"/>
+      <c r="D12" s="125"/>
+      <c r="E12" s="125"/>
       <c r="F12" s="82">
         <f>F10-(F10*F11)</f>
         <v>10.34</v>
@@ -5330,11 +5330,11 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B14" s="11"/>
-      <c r="C14" s="120" t="s">
+      <c r="C14" s="121" t="s">
         <v>103</v>
       </c>
-      <c r="D14" s="121"/>
-      <c r="E14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="123"/>
       <c r="F14" s="76">
         <f>F13*$I$3*$F$12</f>
         <v>398437.12857142865</v>
@@ -5357,11 +5357,11 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B15" s="11"/>
-      <c r="C15" s="120" t="s">
+      <c r="C15" s="121" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="121"/>
-      <c r="E15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="123"/>
       <c r="F15" s="76">
         <f>(1-F13)*$I$3*'Monthly Profit &amp; Refined Data'!$C$8</f>
         <v>64222.619047619053</v>
@@ -5381,62 +5381,62 @@
     </row>
     <row r="18" spans="2:14" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:14" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="114" t="s">
+      <c r="B19" s="115" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="115"/>
-      <c r="D19" s="115"/>
-      <c r="E19" s="115"/>
-      <c r="F19" s="115"/>
-      <c r="G19" s="116"/>
-      <c r="I19" s="114" t="s">
+      <c r="C19" s="116"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="116"/>
+      <c r="G19" s="117"/>
+      <c r="I19" s="115" t="s">
         <v>112</v>
       </c>
-      <c r="J19" s="115"/>
-      <c r="K19" s="115"/>
-      <c r="L19" s="115"/>
-      <c r="M19" s="115"/>
-      <c r="N19" s="116"/>
+      <c r="J19" s="116"/>
+      <c r="K19" s="116"/>
+      <c r="L19" s="116"/>
+      <c r="M19" s="116"/>
+      <c r="N19" s="117"/>
     </row>
     <row r="20" spans="2:14" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="117"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="118"/>
-      <c r="F20" s="118"/>
-      <c r="G20" s="119"/>
-      <c r="I20" s="117"/>
-      <c r="J20" s="118"/>
-      <c r="K20" s="118"/>
-      <c r="L20" s="118"/>
-      <c r="M20" s="118"/>
-      <c r="N20" s="119"/>
+      <c r="B20" s="118"/>
+      <c r="C20" s="119"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="120"/>
+      <c r="I20" s="118"/>
+      <c r="J20" s="119"/>
+      <c r="K20" s="119"/>
+      <c r="L20" s="119"/>
+      <c r="M20" s="119"/>
+      <c r="N20" s="120"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C22" s="134"/>
-      <c r="D22" s="134"/>
+      <c r="C22" s="135"/>
+      <c r="D22" s="135"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C23" s="132" t="s">
+      <c r="C23" s="133" t="s">
         <v>99</v>
       </c>
-      <c r="D23" s="133"/>
+      <c r="D23" s="134"/>
       <c r="E23" s="80">
         <v>0.25</v>
       </c>
-      <c r="K23" s="128" t="s">
+      <c r="K23" s="129" t="s">
         <v>105</v>
       </c>
-      <c r="L23" s="129"/>
+      <c r="L23" s="130"/>
       <c r="M23" s="92">
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C24" s="130" t="s">
+      <c r="C24" s="131" t="s">
         <v>104</v>
       </c>
-      <c r="D24" s="131"/>
+      <c r="D24" s="132"/>
       <c r="E24" s="79">
         <f>E23*I3</f>
         <v>12844.523809523811</v>
@@ -5450,10 +5450,10 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C25" s="112" t="s">
+      <c r="C25" s="113" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="113"/>
+      <c r="D25" s="114"/>
       <c r="E25" s="76">
         <f>E24*'Monthly Profit &amp; Refined Data'!F8</f>
         <v>77067.14285714287</v>
